--- a/output/graficos_regionales/plot_regional_serie_i_ingr_median_a_2024_coquimbo.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_median_a_2024_coquimbo.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:43</t>
+    <t xml:space="preserve">2026-10-05 02:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -492,7 +492,7 @@
         <v>619146</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>627126.62</v>
+        <v>627126.63</v>
       </c>
     </row>
     <row r="5">
